--- a/artfynd/A 28119-2024 artfynd.xlsx
+++ b/artfynd/A 28119-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73920089</v>
+        <v>73920088</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506737.1915237997</v>
+        <v>506755</v>
       </c>
       <c r="R2" t="n">
-        <v>6769458.901319007</v>
+        <v>6769443</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2018-08-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73920092</v>
+        <v>73920090</v>
       </c>
       <c r="B3" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506501.9898014977</v>
+        <v>506757</v>
       </c>
       <c r="R3" t="n">
-        <v>6769459.913362066</v>
+        <v>6769435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2018-08-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-08-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73920086</v>
+        <v>73920087</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506804.0777844564</v>
+        <v>506797</v>
       </c>
       <c r="R4" t="n">
-        <v>6769477.912581036</v>
+        <v>6769465</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2018-08-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-08-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,6 +963,297 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>73920086</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dalarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>506804</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6769478</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>73920089</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dalarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>506737</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6769459</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>73920092</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dalarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>506502</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6769460</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28119-2024 artfynd.xlsx
+++ b/artfynd/A 28119-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73920092</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73920088</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73920090</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73920087</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73920086</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73920089</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>